--- a/Project Outputs for TSI_SAMP_SAMI_V3.4/SAMI_V3.5_FabCheck.xlsx
+++ b/Project Outputs for TSI_SAMP_SAMI_V3.4/SAMI_V3.5_FabCheck.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\CanAssist\Altium\TSI_SAMP_SAMI\Project Outputs for TSI_SAMP_SAMI_V3.4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD3DEAC-CDE2-41A9-B953-3B5F2BCB3A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED23A85-9023-4703-85A1-F94E4D214ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17685" yWindow="0" windowWidth="20820" windowHeight="20985" xr2:uid="{FB73F8E4-5B0A-499D-AD76-FA22E5C8C5A1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{FB73F8E4-5B0A-499D-AD76-FA22E5C8C5A1}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMI_V3.5" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="344">
   <si>
     <t>Name</t>
   </si>
@@ -1071,12 +1071,6 @@
   </si>
   <si>
     <t>Placed</t>
-  </si>
-  <si>
-    <t>Not in stock, ~15 in inventory</t>
-  </si>
-  <si>
-    <t>Received from Mouser</t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1100,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1129,31 +1123,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -1168,8 +1142,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1504,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4DC37E-2EE5-40BA-BB89-F354D725F7F7}">
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
@@ -2865,7 +2837,7 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>321</v>
       </c>
@@ -2893,7 +2865,7 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>331</v>
       </c>
@@ -2921,7 +2893,7 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>336</v>
       </c>
@@ -2949,7 +2921,7 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>22</v>
       </c>
@@ -2976,11 +2948,8 @@
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
-      <c r="K52" s="8" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>56</v>
       </c>
@@ -3007,11 +2976,8 @@
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-      <c r="K53" s="8" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>134</v>
       </c>
@@ -3038,11 +3004,8 @@
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-      <c r="K54" s="8" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>140</v>
       </c>
@@ -3069,11 +3032,8 @@
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
-      <c r="K55" s="9" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>157</v>
       </c>
@@ -3100,11 +3060,8 @@
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
-      <c r="K56" s="9" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>169</v>
       </c>
@@ -3131,11 +3088,8 @@
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
-      <c r="K57" s="9" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>174</v>
       </c>
@@ -3162,11 +3116,8 @@
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
-      <c r="K58" s="9" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>199</v>
       </c>
@@ -3193,11 +3144,8 @@
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
-      <c r="K59" s="9" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>209</v>
       </c>
@@ -3224,12 +3172,8 @@
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
-      <c r="K60" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="L60" s="9"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>260</v>
       </c>
@@ -3256,11 +3200,8 @@
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
-      <c r="K61" s="9" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>305</v>
       </c>
@@ -3287,11 +3228,8 @@
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
-      <c r="K62" s="9" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>311</v>
       </c>
@@ -3318,11 +3256,8 @@
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
-      <c r="K63" s="9" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>326</v>
       </c>
@@ -3349,9 +3284,6 @@
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
-      <c r="K64" s="9" t="s">
-        <v>345</v>
-      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H64">

--- a/Project Outputs for TSI_SAMP_SAMI_V3.4/SAMI_V3.5_FabCheck.xlsx
+++ b/Project Outputs for TSI_SAMP_SAMI_V3.4/SAMI_V3.5_FabCheck.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\CanAssist\Altium\TSI_SAMP_SAMI\Project Outputs for TSI_SAMP_SAMI_V3.4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED23A85-9023-4703-85A1-F94E4D214ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD3DEAC-CDE2-41A9-B953-3B5F2BCB3A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{FB73F8E4-5B0A-499D-AD76-FA22E5C8C5A1}"/>
+    <workbookView xWindow="17685" yWindow="0" windowWidth="20820" windowHeight="20985" xr2:uid="{FB73F8E4-5B0A-499D-AD76-FA22E5C8C5A1}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMI_V3.5" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="346">
   <si>
     <t>Name</t>
   </si>
@@ -1071,6 +1071,12 @@
   </si>
   <si>
     <t>Placed</t>
+  </si>
+  <si>
+    <t>Not in stock, ~15 in inventory</t>
+  </si>
+  <si>
+    <t>Received from Mouser</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1106,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1123,11 +1129,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -1142,6 +1168,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1476,7 +1504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4DC37E-2EE5-40BA-BB89-F354D725F7F7}">
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
@@ -2837,7 +2865,7 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>321</v>
       </c>
@@ -2865,7 +2893,7 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>331</v>
       </c>
@@ -2893,7 +2921,7 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>336</v>
       </c>
@@ -2921,7 +2949,7 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>22</v>
       </c>
@@ -2948,8 +2976,11 @@
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K52" s="8" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>56</v>
       </c>
@@ -2976,8 +3007,11 @@
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K53" s="8" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>134</v>
       </c>
@@ -3004,8 +3038,11 @@
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K54" s="8" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>140</v>
       </c>
@@ -3032,8 +3069,11 @@
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K55" s="9" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>157</v>
       </c>
@@ -3060,8 +3100,11 @@
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K56" s="9" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>169</v>
       </c>
@@ -3088,8 +3131,11 @@
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K57" s="9" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>174</v>
       </c>
@@ -3116,8 +3162,11 @@
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K58" s="9" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>199</v>
       </c>
@@ -3144,8 +3193,11 @@
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K59" s="9" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>209</v>
       </c>
@@ -3172,8 +3224,12 @@
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K60" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="L60" s="9"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>260</v>
       </c>
@@ -3200,8 +3256,11 @@
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K61" s="9" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>305</v>
       </c>
@@ -3228,8 +3287,11 @@
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K62" s="9" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>311</v>
       </c>
@@ -3256,8 +3318,11 @@
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K63" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>326</v>
       </c>
@@ -3284,6 +3349,9 @@
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
+      <c r="K64" s="9" t="s">
+        <v>345</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H64">
